--- a/Project 1 Data Quality Assessment/D7 Topological Role Consistency and Structural Representativeness/outputs/local/D7_topology_drift_alerts.xlsx
+++ b/Project 1 Data Quality Assessment/D7 Topological Role Consistency and Structural Representativeness/outputs/local/D7_topology_drift_alerts.xlsx
@@ -431,7 +431,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="33" customWidth="1" min="2" max="2"/>
     <col width="19" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
@@ -526,7 +526,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>d7-topology-declared-v1</t>
+          <t>d7-topology-author-confirmed-v2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -571,7 +571,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -588,7 +588,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>d7-topology-declared-v1</t>
+          <t>d7-topology-author-confirmed-v2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>d7-topology-declared-v1</t>
+          <t>d7-topology-author-confirmed-v2</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -712,7 +712,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>d7-topology-declared-v1</t>
+          <t>d7-topology-author-confirmed-v2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -757,7 +757,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>d7-topology-declared-v1</t>
+          <t>d7-topology-author-confirmed-v2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -836,7 +836,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>d7-topology-declared-v1</t>
+          <t>d7-topology-author-confirmed-v2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>d7-topology-declared-v1</t>
+          <t>d7-topology-author-confirmed-v2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -943,7 +943,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -960,7 +960,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>d7-topology-declared-v1</t>
+          <t>d7-topology-author-confirmed-v2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1005,7 +1005,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>d7-topology-declared-v1</t>
+          <t>d7-topology-author-confirmed-v2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>d7-topology-declared-v1</t>
+          <t>d7-topology-author-confirmed-v2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>d7-topology-declared-v1</t>
+          <t>d7-topology-author-confirmed-v2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>d7-topology-declared-v1</t>
+          <t>d7-topology-author-confirmed-v2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>d7-topology-declared-v1</t>
+          <t>d7-topology-author-confirmed-v2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1315,7 +1315,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>d7-topology-declared-v1</t>
+          <t>d7-topology-author-confirmed-v2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1377,7 +1377,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1394,7 +1394,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>d7-topology-declared-v1</t>
+          <t>d7-topology-author-confirmed-v2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>d7-topology-declared-v1</t>
+          <t>d7-topology-author-confirmed-v2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1518,7 +1518,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>d7-topology-declared-v1</t>
+          <t>d7-topology-author-confirmed-v2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1563,7 +1563,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>d7-topology-declared-v1</t>
+          <t>d7-topology-author-confirmed-v2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1625,7 +1625,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1642,7 +1642,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>d7-topology-declared-v1</t>
+          <t>d7-topology-author-confirmed-v2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1687,7 +1687,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>d7-topology-declared-v1</t>
+          <t>d7-topology-author-confirmed-v2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1749,7 +1749,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>d7-topology-declared-v1</t>
+          <t>d7-topology-author-confirmed-v2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1811,7 +1811,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -1828,7 +1828,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>d7-topology-declared-v1</t>
+          <t>d7-topology-author-confirmed-v2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1873,7 +1873,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>d7-topology-declared-v1</t>
+          <t>d7-topology-author-confirmed-v2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>d7-topology-declared-v1</t>
+          <t>d7-topology-author-confirmed-v2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1997,7 +1997,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2014,7 +2014,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>d7-topology-declared-v1</t>
+          <t>d7-topology-author-confirmed-v2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -2076,7 +2076,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>d7-topology-declared-v1</t>
+          <t>d7-topology-author-confirmed-v2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>d7-topology-declared-v1</t>
+          <t>d7-topology-author-confirmed-v2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2183,7 +2183,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2200,7 +2200,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>d7-topology-declared-v1</t>
+          <t>d7-topology-author-confirmed-v2</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2245,7 +2245,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>d7-topology-declared-v1</t>
+          <t>d7-topology-author-confirmed-v2</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2307,7 +2307,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>d7-topology-declared-v1</t>
+          <t>d7-topology-author-confirmed-v2</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2369,7 +2369,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>d7-topology-declared-v1</t>
+          <t>d7-topology-author-confirmed-v2</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2431,7 +2431,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -2448,7 +2448,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>d7-topology-declared-v1</t>
+          <t>d7-topology-author-confirmed-v2</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2493,7 +2493,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>d7-topology-declared-v1</t>
+          <t>d7-topology-author-confirmed-v2</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2555,7 +2555,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -2572,7 +2572,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>d7-topology-declared-v1</t>
+          <t>d7-topology-author-confirmed-v2</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -2634,7 +2634,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>d7-topology-declared-v1</t>
+          <t>d7-topology-author-confirmed-v2</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -2696,7 +2696,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>d7-topology-declared-v1</t>
+          <t>d7-topology-author-confirmed-v2</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2741,7 +2741,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -2758,7 +2758,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>d7-topology-declared-v1</t>
+          <t>d7-topology-author-confirmed-v2</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2803,7 +2803,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>d7-topology-declared-v1</t>
+          <t>d7-topology-author-confirmed-v2</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2865,7 +2865,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -2882,7 +2882,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>d7-topology-declared-v1</t>
+          <t>d7-topology-author-confirmed-v2</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2927,7 +2927,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -2944,7 +2944,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>d7-topology-declared-v1</t>
+          <t>d7-topology-author-confirmed-v2</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>d7-topology-declared-v1</t>
+          <t>d7-topology-author-confirmed-v2</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>d7-topology-declared-v1</t>
+          <t>d7-topology-author-confirmed-v2</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3113,7 +3113,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -3130,7 +3130,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>d7-topology-declared-v1</t>
+          <t>d7-topology-author-confirmed-v2</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -3192,7 +3192,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>d7-topology-declared-v1</t>
+          <t>d7-topology-author-confirmed-v2</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3237,7 +3237,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -3254,7 +3254,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>d7-topology-declared-v1</t>
+          <t>d7-topology-author-confirmed-v2</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3299,7 +3299,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -3316,7 +3316,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>d7-topology-declared-v1</t>
+          <t>d7-topology-author-confirmed-v2</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3361,7 +3361,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -3378,7 +3378,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>d7-topology-declared-v1</t>
+          <t>d7-topology-author-confirmed-v2</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3423,7 +3423,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -3440,7 +3440,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>d7-topology-declared-v1</t>
+          <t>d7-topology-author-confirmed-v2</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3485,7 +3485,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -3502,7 +3502,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>d7-topology-declared-v1</t>
+          <t>d7-topology-author-confirmed-v2</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3547,7 +3547,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>d7-topology-declared-v1</t>
+          <t>d7-topology-author-confirmed-v2</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3609,7 +3609,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -3626,7 +3626,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>d7-topology-declared-v1</t>
+          <t>d7-topology-author-confirmed-v2</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -3688,7 +3688,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>d7-topology-declared-v1</t>
+          <t>d7-topology-author-confirmed-v2</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3733,7 +3733,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>d7-topology-declared-v1</t>
+          <t>d7-topology-author-confirmed-v2</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3795,7 +3795,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -3812,7 +3812,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>d7-topology-declared-v1</t>
+          <t>d7-topology-author-confirmed-v2</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3857,7 +3857,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
